--- a/artfynd/A 65581-2020 artfynd.xlsx
+++ b/artfynd/A 65581-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65581-2020 artfynd.xlsx
+++ b/artfynd/A 65581-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,6 +924,130 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118955211</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97853</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Enesberg, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>359114</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6393133</v>
+      </c>
+      <c r="S4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65581-2020 artfynd.xlsx
+++ b/artfynd/A 65581-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1048,103 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129949531</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>359129</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6393136</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65581-2020 artfynd.xlsx
+++ b/artfynd/A 65581-2020 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>129949531</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 65581-2020 artfynd.xlsx
+++ b/artfynd/A 65581-2020 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>129949531</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
